--- a/astro-site/public/dl/restaurant-financial-plan-templates/06-restaurant-kpi-ratios-dashboard.xlsx
+++ b/astro-site/public/dl/restaurant-financial-plan-templates/06-restaurant-kpi-ratios-dashboard.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -305,6 +305,9 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="8" fillId="11" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
@@ -316,6 +319,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,7 +449,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Your value vs industry target</a:t>
+              <a:t>Your value vs kit target</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -869,7 +875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B24"/>
+  <dimension ref="A2:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -949,7 +955,7 @@
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>▸ GOP %: target &gt; 20% · danger &lt; 15% (the numbers live in "Benchmarks" F:G).</t>
+          <t>▸ GOP %: target &gt; 21% · danger &lt; 16% (the numbers live in "Benchmarks" F:G).</t>
         </is>
       </c>
     </row>
@@ -959,7 +965,7 @@
     <row r="19">
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>▸ RevPASH is measured per SEAT and hour (seating capacity × service hours), not per sq ft. "Service hours" are the hours when guests are seated (e.g. 6 hours/day × 26 days = 156), not the hours the restaurant is open. Sales per sq ft have their own row.</t>
+          <t>▸ RevPASH is measured per SEAT and hour (seating capacity × service hours), not per sq ft. "Service hours" are the hours when guests are seated (e.g. 6 hours/day × 26 days = 156), not the hours the restaurant is open. Sales per sq ft have their own row, as an annual figure.</t>
         </is>
       </c>
     </row>
@@ -988,6 +994,13 @@
       <c r="B24" s="20" t="inlineStr">
         <is>
           <t>Version 2.0 · October 2026 · aichef.pro/en/digital-products/restaurant-financial-plan-templates · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>Planning tool, not financial, tax or legal advice. Requirements vary by state and city — check with your accountant and local authorities.</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1090,7 @@
           <t>Total sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="C6" s="43" t="n">
+      <c r="C6" s="44" t="n">
         <v>31460</v>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -1092,7 +1105,7 @@
           <t>· of which, bar / beverage (excl. sales tax)</t>
         </is>
       </c>
-      <c r="C7" s="43" t="n">
+      <c r="C7" s="44" t="n">
         <v>7865</v>
       </c>
       <c r="D7" s="10" t="inlineStr">
@@ -1107,7 +1120,7 @@
           <t>Food cost — usage</t>
         </is>
       </c>
-      <c r="C8" s="44">
+      <c r="C8" s="45">
         <f>IFERROR($C$33+$C$34-$C$35,0)</f>
         <v>7078.5</v>
       </c>
@@ -1123,7 +1136,7 @@
           <t>Total operating expenses</t>
         </is>
       </c>
-      <c r="C9" s="44">
+      <c r="C9" s="45">
         <f>IFERROR($C$8+$C$36+$C$10+$C$37,0)</f>
         <v>23017.6</v>
       </c>
@@ -1139,7 +1152,7 @@
           <t>Total labor cost</t>
         </is>
       </c>
-      <c r="C10" s="43" t="n">
+      <c r="C10" s="44" t="n">
         <v>8808.799999999999</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -1214,9 +1227,9 @@
           <t>Your Value</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
-        <is>
-          <t>Industry Benchmark</t>
+      <c r="D16" s="34" t="inlineStr">
+        <is>
+          <t>Kit benchmark (editable estimate)</t>
         </is>
       </c>
       <c r="E16" s="26" t="inlineStr">
@@ -1311,7 +1324,7 @@
       </c>
       <c r="D20" s="28" t="str">
         <f>Benchmarks!$D$7</f>
-        <v>15% - 20%</v>
+        <v>16% - 21%</v>
       </c>
       <c r="E20" s="15" t="str">
         <f>IFERROR(IF(ISNUMBER($C20),IF($C20&gt;Benchmarks!$F$7,"✅ Healthy",IF($C20&gt;=Benchmarks!$G$7,"⚠️ Tight","🔴 Danger")),"—"),"—")</f>
@@ -1319,7 +1332,7 @@
       </c>
       <c r="F20" s="29">
         <f>Benchmarks!$F$7</f>
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="21">
@@ -1351,7 +1364,7 @@
           <t>RevPASH (per seat-hour)</t>
         </is>
       </c>
-      <c r="C22" s="45">
+      <c r="C22" s="46">
         <f>IFERROR($C$6/($C$13*$C$12),"Enter seats and hours")</f>
         <v>3.361111111111111</v>
       </c>
@@ -1363,7 +1376,7 @@
         <f>IFERROR(IF(ISNUMBER($C22),IF($C22&gt;Benchmarks!$F$13,"✅ Healthy",IF($C22&gt;=Benchmarks!$G$13,"⚠️ Tight","🔴 Danger")),"—"),"—")</f>
         <v>⚠️ Tight</v>
       </c>
-      <c r="F22" s="46">
+      <c r="F22" s="47">
         <f>Benchmarks!$F$13</f>
         <v>6.0</v>
       </c>
@@ -1437,6 +1450,29 @@
         <v>0.7</v>
       </c>
     </row>
+    <row r="26">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Occupancy (rent) / Sales</t>
+        </is>
+      </c>
+      <c r="C26" s="29">
+        <f>IFERROR($C$38/$C$6,"Enter sales")</f>
+        <v>0.09535918626827718</v>
+      </c>
+      <c r="D26" s="31" t="str">
+        <f>Benchmarks!$D$8</f>
+        <v>6% - 10%</v>
+      </c>
+      <c r="E26" t="str">
+        <f>IFERROR(IF(ISNUMBER($C26),IF($C26&lt;Benchmarks!$F$8,"✅ Excellent",IF($C26&lt;=Benchmarks!$G$8,"⚠️ Acceptable","🔴 High")),"—"),"—")</f>
+        <v>⚠️ Acceptable</v>
+      </c>
+      <c r="F26" s="29">
+        <f>Benchmarks!$F$8</f>
+        <v>0.06</v>
+      </c>
+    </row>
     <row r="27">
       <c r="A27" s="10" t="n"/>
       <c r="B27" s="6" t="inlineStr">
@@ -1451,7 +1487,7 @@
           <t>Cost per cover</t>
         </is>
       </c>
-      <c r="C28" s="46">
+      <c r="C28" s="47">
         <f>IFERROR($C$9/$C$14,"Enter covers")</f>
         <v>16.096223776223777</v>
       </c>
@@ -1462,20 +1498,20 @@
           <t>Average check (excl. sales tax)</t>
         </is>
       </c>
-      <c r="C29" s="46">
+      <c r="C29" s="47">
         <f>IFERROR($C$6/$C$14,"Enter covers")</f>
         <v>22.0</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Sales per sq ft (excl. sales tax)</t>
-        </is>
-      </c>
-      <c r="C30" s="46">
-        <f>IFERROR($C$6/$C$11,"Enter the dining room sq ft")</f>
-        <v>36.58139534883721</v>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Annual sales per sq ft (excl. sales tax)</t>
+        </is>
+      </c>
+      <c r="C30" s="47">
+        <f>IFERROR($C$6*12/$C$11,"Enter the dining room sq ft")</f>
+        <v>438.9767441860465</v>
       </c>
     </row>
     <row r="32">
@@ -1491,7 +1527,7 @@
           <t>Opening food inventory</t>
         </is>
       </c>
-      <c r="C33" s="43" t="n">
+      <c r="C33" s="44" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="32" t="inlineStr">
@@ -1506,7 +1542,7 @@
           <t>Food purchases for the period</t>
         </is>
       </c>
-      <c r="C34" s="43" t="n">
+      <c r="C34" s="44" t="n">
         <v>7078.5</v>
       </c>
       <c r="D34" s="32" t="inlineStr">
@@ -1521,7 +1557,7 @@
           <t>Ending food inventory</t>
         </is>
       </c>
-      <c r="C35" s="43" t="n">
+      <c r="C35" s="44" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="32" t="inlineStr">
@@ -1536,7 +1572,7 @@
           <t>Beverage cost — usage</t>
         </is>
       </c>
-      <c r="C36" s="43" t="n">
+      <c r="C36" s="44" t="n">
         <v>1730.3</v>
       </c>
       <c r="D36" s="32" t="inlineStr">
@@ -1551,7 +1587,7 @@
           <t>Other operating expenses</t>
         </is>
       </c>
-      <c r="C37" s="43" t="n">
+      <c r="C37" s="44" t="n">
         <v>5400</v>
       </c>
       <c r="D37" s="32" t="inlineStr">
@@ -1566,7 +1602,7 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="C38" s="43" t="n">
+      <c r="C38" s="44" t="n">
         <v>3000</v>
       </c>
       <c r="D38" s="32" t="inlineStr">
@@ -1595,7 +1631,7 @@
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E17:E25">
+  <conditionalFormatting sqref="E17:E26">
     <cfRule type="containsText" priority="1" operator="containsText" dxfId="0" stopIfTrue="1" text="🔴 High">
       <formula>NOT(ISERROR(SEARCH("🔴 High",E17)))</formula>
     </cfRule>
@@ -1657,7 +1693,7 @@
     <row r="1">
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>Restaurant Industry Benchmarks</t>
+          <t>Kit Benchmarks (editable estimates)</t>
         </is>
       </c>
     </row>
@@ -1806,24 +1842,24 @@
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>&gt; 20%</t>
+          <t>&gt; 21%</t>
         </is>
       </c>
       <c r="D7" s="37" t="inlineStr">
         <is>
-          <t>15% - 20%</t>
+          <t>16% - 21%</t>
         </is>
       </c>
       <c r="E7" s="38" t="inlineStr">
         <is>
-          <t>&lt; 15%</t>
+          <t>&lt; 16%</t>
         </is>
       </c>
       <c r="F7" s="29" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H7" s="39" t="inlineStr">
         <is>
@@ -1867,7 +1903,7 @@
     <row r="9">
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Marketing / Sales</t>
+          <t>Marketing / Sales (reference only)</t>
         </is>
       </c>
       <c r="C9" s="36" t="inlineStr">
@@ -1999,7 +2035,7 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>RevPASH (per seat-hour)</t>
+          <t>RevPASH (per seat-hour, your market)</t>
         </is>
       </c>
       <c r="C13" s="40" t="inlineStr">
@@ -2017,10 +2053,10 @@
           <t>&lt; 3</t>
         </is>
       </c>
-      <c r="F13" s="46" t="n">
+      <c r="F13" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="G13" s="46" t="n">
+      <c r="G13" s="47" t="n">
         <v>3</v>
       </c>
       <c r="H13" s="39" t="inlineStr">
@@ -2063,10 +2099,24 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="73.5" customHeight="1">
       <c r="B17" s="32" t="inlineStr">
         <is>
           <t>The "Target (no.)" and "Limit (no.)" columns are the kit's ONLY source of thresholds: the traffic light in the "Ratios" tab reads them. The text columns on the left are a reading guide: if you edit the numbers, update them too.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36.75" customHeight="1">
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>RevPASH thresholds (6 and 3 per seat-hour) assume US dollars: set them for your currency and market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36.75" customHeight="1">
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>GOP thresholds (21% / 16%) = EBITDA thresholds (15% / 10%) + 6 points of occupancy (rent).</t>
         </is>
       </c>
     </row>
